--- a/templates/excel/klarna-test.xlsx
+++ b/templates/excel/klarna-test.xlsx
@@ -11,8 +11,8 @@
     <sheet name="Klarna_Score" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Quality_Gates" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Reversal_Plan" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="README" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="_metadata" sheetId="6" state="hidden" r:id="rId6"/>
+    <sheet name="_metadata" sheetId="5" state="hidden" r:id="rId5"/>
+    <sheet name="README" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,7 +21,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -60,11 +62,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -576,10 +579,8 @@
         <f>IF(ISBLANK(H2),"",IF(H2&gt;=14,"PROCEED","HOLD"))</f>
         <v/>
       </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
+      <c r="K2" s="2" t="n">
+        <v>46246</v>
       </c>
     </row>
   </sheetData>
@@ -593,7 +594,7 @@
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:K1000">
     <cfRule type="expression" priority="3" dxfId="1">
-      <formula>AND(K2&lt;TODAY(),L2="")</formula>
+      <formula>AND(K2&lt;&gt;"",K2&lt;TODAY(),L2="")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
@@ -859,11 +860,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L1000">
-    <cfRule type="cellIs" priority="31" operator="lessThan" dxfId="1">
-      <formula>14</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="32" operator="greaterThanOrEqual" dxfId="0">
-      <formula>14</formula>
+    <cfRule type="expression" priority="31" dxfId="1">
+      <formula>AND($A2&lt;&gt;"",L2&lt;14)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="32" dxfId="0">
+      <formula>AND($A2&lt;&gt;"",L2&gt;=14)</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="11">
@@ -1065,150 +1066,66 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A23"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="110" customWidth="1" min="1" max="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t># klarna-test.xlsx</t>
+          <t>key</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>value</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>spec_version</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>1.0.0</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>PURPOSE</t>
+          <t>generation_date</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Operational scoring of the framework's signature epistemic check. Triggered by Routine R7 on `ai-replaces-human` PR labels; also used manually for non-PR decisions.</t>
+          <t>oot_version</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>1.0.0</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>WRITTEN BY</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>- Routine R7 (Klarna Test Trigger) — appends rows to Decision_Log on PR-label events.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>- Manual scoring by the assigned scorer + non-beneficiary reviewer in Klarna_Score.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>READ BY</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>- Routine R7 — the `oot/klarna-test` GitHub status check workflow polls Klarna_Score for the matching test_id; sets the check passing only when total_score &gt;= 14 AND scorer_signoff = Yes AND non_beneficiary_signoff = Yes.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>- Routine R6 (Daily Audit Trail) — references Klarna Test entries.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>- Routine R2 (Weekly BR Prep) — surfaces open + recently-resolved tests in the Klarna_Test_Hits mirror in X3.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>VALIDATION</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>- Each Q column accepts only 0, 1, or 2.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>- No "n/a" affordance — every question always applies. Q8 (public-communication posture) explicitly requires "no comms" to be itself a written, owned posture to score 2.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>DO NOT</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>- Bypass the discipline. The Klarna Test is non-negotiable.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>- Score with a beneficiary as the non-beneficiary reviewer (Q7).</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>- Flip total_score &gt;= 14 by rationalising 1s into 2s. The pre-committed remediation flow exists for tests that score below threshold.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>- Modify completed (signed-off) Klarna_Score rows. Re-scores after remediation update the SAME row; do not create a new test_id.</t>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>file_id</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>X4</t>
         </is>
       </c>
     </row>
@@ -1223,66 +1140,150 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:A23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="110" customWidth="1" min="1" max="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>key</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>value</t>
+          <t># klarna-test.xlsx</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>spec_version</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>1.0.0</t>
-        </is>
-      </c>
+      <c r="A2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>generation_date</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
+          <t>PURPOSE</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>oot_version</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>1.0.0</t>
+          <t>Operational scoring of the framework's signature epistemic check. Triggered by Routine R7 on `ai-replaces-human` PR labels; also used manually for non-PR decisions.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>file_id</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>X4</t>
+      <c r="A5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>WRITTEN BY</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>- Routine R7 (Klarna Test Trigger) — appends rows to Decision_Log on PR-label events.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>- Manual scoring by the assigned scorer + non-beneficiary reviewer in Klarna_Score.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>READ BY</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>- Routine R7 — the `oot/klarna-test` GitHub status check workflow polls Klarna_Score for the matching test_id; sets the check passing only when total_score &gt;= 14 AND scorer_signoff = Yes AND non_beneficiary_signoff = Yes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>- Routine R6 (Daily Audit Trail) — references Klarna Test entries.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>- Routine R2 (Weekly BR Prep) — surfaces open + recently-resolved tests in the Klarna_Test_Hits mirror in X3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>VALIDATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>- Each Q column accepts only 0, 1, or 2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>- No "n/a" affordance — every question always applies. Q8 (public-communication posture) explicitly requires "no comms" to be itself a written, owned posture to score 2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>DO NOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>- Bypass the discipline. The Klarna Test is non-negotiable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>- Score with a beneficiary as the non-beneficiary reviewer (Q7).</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>- Flip total_score &gt;= 14 by rationalising 1s into 2s. The pre-committed remediation flow exists for tests that score below threshold.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>- Modify completed (signed-off) Klarna_Score rows. Re-scores after remediation update the SAME row; do not create a new test_id.</t>
         </is>
       </c>
     </row>

--- a/templates/excel/klarna-test.xlsx
+++ b/templates/excel/klarna-test.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:M2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -471,6 +471,7 @@
     <col width="28" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
     <col width="30" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -534,6 +535,11 @@
           <t>post_review_outcome</t>
         </is>
       </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -581,6 +587,11 @@
       </c>
       <c r="K2" s="2" t="n">
         <v>46246</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>monitoring</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -597,9 +608,12 @@
       <formula>AND(K2&lt;&gt;"",K2&lt;TODAY(),L2="")</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="1">
+  <dataValidations count="2">
     <dataValidation sqref="D2:D1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"pr_label,manual,pre_rollout"</formula1>
+    </dataValidation>
+    <dataValidation sqref="M2:M1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Klarna lifecycle status" prompt="Lifecycle state (not the score verdict). R7 writes 'scoring' on create; transitions to proceeded/remediation/held then monitoring. See ADR-004." type="list">
+      <formula1>"scoring,remediation,monitoring,proceeded,held"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1140,7 +1154,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A23"/>
+  <dimension ref="A1:A29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -1231,57 +1245,95 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>VALIDATION</t>
+          <t>SCHEMA — decision (I) vs status (M) (ADR-004)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>- Each Q column accepts only 0, 1, or 2.</t>
+          <t>- Decision_Log column I (decision) is the THRESHOLD VERDICT: =IF(H&gt;=14,"PROCEED","HOLD"), formula-driven.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>- No "n/a" affordance — every question always applies. Q8 (public-communication posture) explicitly requires "no comms" to be itself a written, owned posture to score 2.</t>
+          <t>- Decision_Log column M (status) is the LIFECYCLE STATE: a literal enum (scoring | remediation | monitoring | proceeded | held), never a formula. R7 writes 'scoring' on create; the scoring outcome moves it to proceeded/remediation/held; proceeded rows become 'monitoring' until the K review date passes.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr"/>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>- I and M may disagree transiently (e.g. I=PROCEED while M=monitoring during the 90-day window). The oot/klarna-test gate reads Klarna_Score directly and never consults status.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>DO NOT</t>
-        </is>
-      </c>
+      <c r="A19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>- Bypass the discipline. The Klarna Test is non-negotiable.</t>
+          <t>VALIDATION</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>- Score with a beneficiary as the non-beneficiary reviewer (Q7).</t>
+          <t>- Each Q column accepts only 0, 1, or 2.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>- Flip total_score &gt;= 14 by rationalising 1s into 2s. The pre-committed remediation flow exists for tests that score below threshold.</t>
+          <t>- No "n/a" affordance — every question always applies. Q8 (public-communication posture) explicitly requires "no comms" to be itself a written, owned posture to score 2.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
+        <is>
+          <t>- Decision_Log column M (status) accepts only the five lifecycle enum values.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>DO NOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>- Bypass the discipline. The Klarna Test is non-negotiable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>- Score with a beneficiary as the non-beneficiary reviewer (Q7).</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>- Flip total_score &gt;= 14 by rationalising 1s into 2s. The pre-committed remediation flow exists for tests that score below threshold.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
         <is>
           <t>- Modify completed (signed-off) Klarna_Score rows. Re-scores after remediation update the SAME row; do not create a new test_id.</t>
         </is>
